--- a/2025-MLS-projections/BSIA Catch/CatchbyFleetGroup.xlsx
+++ b/2025-MLS-projections/BSIA Catch/CatchbyFleetGroup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jon.brodziak\Desktop\2024 WCNPO MLS Rebuilding\2025 MLS projections\BSIA Catch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CC8FF1-AE03-41E6-AA2A-6CA870E7F06A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF96F18-5BFC-4670-B31B-353ADE44580F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8863" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="754" yWindow="754" windowWidth="12343" windowHeight="7423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CatchbyFleetGroup" sheetId="8" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="36">
   <si>
     <t>Year</t>
   </si>
@@ -2799,6 +2799,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B11889C-8E73-4A4E-ADA6-2073688C0066}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:Y78"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
@@ -2818,6 +2821,17 @@
       </c>
     </row>
     <row r="2" spans="1:25" s="1" customFormat="1" ht="26.15" x14ac:dyDescent="0.7">
+      <c r="C2" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
       <c r="P2" s="42" t="s">
         <v>24</v>
       </c>
@@ -2831,6 +2845,33 @@
       <c r="X2" s="42"/>
     </row>
     <row r="3" spans="1:25" ht="18.45" x14ac:dyDescent="0.5">
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="P3" s="2" t="s">
         <v>12</v>
       </c>
@@ -2860,6 +2901,15 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="18.45" x14ac:dyDescent="0.5">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
@@ -2901,32 +2951,32 @@
       <c r="B6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
-        <v>2</v>
-      </c>
-      <c r="E6" s="2">
-        <v>4</v>
-      </c>
-      <c r="F6" s="2">
-        <v>5</v>
-      </c>
-      <c r="G6" s="2">
-        <v>6</v>
-      </c>
-      <c r="H6" s="2">
-        <v>13</v>
-      </c>
-      <c r="I6" s="2">
-        <v>14</v>
-      </c>
-      <c r="J6" s="2">
-        <v>16</v>
-      </c>
-      <c r="K6" s="2">
-        <v>18</v>
+      <c r="C6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>2</v>
@@ -8108,15 +8158,16 @@
       <c r="Y78" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="C5:K5"/>
     <mergeCell ref="P5:X5"/>
     <mergeCell ref="P65:X65"/>
     <mergeCell ref="P62:X62"/>
     <mergeCell ref="P2:X2"/>
+    <mergeCell ref="C2:K2"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="44" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
